--- a/diseases/d063/2015-2019.xlsx
+++ b/diseases/d063/2015-2019.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21770,7 +21770,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23603,7 +23603,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25436,7 +25436,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -26658,7 +26658,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27269,7 +27269,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -27880,7 +27880,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29102,7 +29102,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33379,7 +33379,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -35212,7 +35212,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35823,7 +35823,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -36434,7 +36434,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">

--- a/diseases/d063/2015-2019.xlsx
+++ b/diseases/d063/2015-2019.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21770,7 +21770,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23603,7 +23603,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25436,7 +25436,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -26658,7 +26658,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27269,7 +27269,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -27880,7 +27880,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29102,7 +29102,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33379,7 +33379,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -35212,7 +35212,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35823,7 +35823,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -36434,7 +36434,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">

--- a/diseases/d063/2015-2019.xlsx
+++ b/diseases/d063/2015-2019.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16281,7 +16281,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17503,7 +17503,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -21169,7 +21169,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -21780,7 +21780,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -23002,7 +23002,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23613,7 +23613,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24835,7 +24835,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -25446,7 +25446,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN126" t="b">
@@ -26668,7 +26668,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -27890,7 +27890,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -28501,7 +28501,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -29112,7 +29112,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -29723,7 +29723,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -30334,7 +30334,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30945,7 +30945,7 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN150" t="b">
@@ -31556,7 +31556,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -32167,7 +32167,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -32778,7 +32778,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -33389,7 +33389,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -34000,7 +34000,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -34611,7 +34611,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -35222,7 +35222,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -35833,7 +35833,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -36444,7 +36444,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -37055,7 +37055,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN180" t="b">

--- a/diseases/d063/2015-2019.xlsx
+++ b/diseases/d063/2015-2019.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21770,7 +21770,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23603,7 +23603,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25436,7 +25436,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -26658,7 +26658,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27269,7 +27269,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -27880,7 +27880,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29102,7 +29102,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33379,7 +33379,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -35212,7 +35212,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35823,7 +35823,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -36434,7 +36434,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">

--- a/diseases/d063/2015-2019.xlsx
+++ b/diseases/d063/2015-2019.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21770,7 +21770,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23603,7 +23603,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25436,7 +25436,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -26658,7 +26658,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27269,7 +27269,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -27880,7 +27880,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29102,7 +29102,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33379,7 +33379,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -35212,7 +35212,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35823,7 +35823,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -36434,7 +36434,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">

--- a/diseases/d063/2015-2019.xlsx
+++ b/diseases/d063/2015-2019.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21770,7 +21770,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23603,7 +23603,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25436,7 +25436,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -26658,7 +26658,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27269,7 +27269,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -27880,7 +27880,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29102,7 +29102,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33379,7 +33379,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -35212,7 +35212,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35823,7 +35823,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -36434,7 +36434,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">

--- a/diseases/d063/2015-2019.xlsx
+++ b/diseases/d063/2015-2019.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15049,7 +15049,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19937,7 +19937,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -21770,7 +21770,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23603,7 +23603,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25436,7 +25436,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -26658,7 +26658,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27269,7 +27269,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -27880,7 +27880,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29102,7 +29102,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -33379,7 +33379,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -35212,7 +35212,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35823,7 +35823,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -36434,7 +36434,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
